--- a/output/palmer_drought_trendlines/region/Half-Decade.xlsx
+++ b/output/palmer_drought_trendlines/region/Half-Decade.xlsx
@@ -55,136 +55,136 @@
     <t>West Region</t>
   </si>
   <si>
+    <t>Great Basin</t>
+  </si>
+  <si>
+    <t>California River Basin</t>
+  </si>
+  <si>
     <t>US Rockies and Westward</t>
   </si>
   <si>
-    <t>Great Basin</t>
+    <t>Rio Grande River Basin</t>
   </si>
   <si>
     <t>NWS Western Region</t>
   </si>
   <si>
-    <t>California River Basin</t>
-  </si>
-  <si>
-    <t>Rio Grande River Basin</t>
+    <t>Spring Wheat Belt (area weighted)</t>
   </si>
   <si>
     <t>West North Central Region</t>
   </si>
   <si>
-    <t>Spring Wheat Belt (area weighted)</t>
-  </si>
-  <si>
     <t>Cotton Belt (area weighted)</t>
   </si>
   <si>
     <t>Missouri River Basin</t>
   </si>
   <si>
+    <t>Great Plains</t>
+  </si>
+  <si>
     <t>Pacific Northwest Basin</t>
   </si>
   <si>
-    <t>Great Plains</t>
-  </si>
-  <si>
     <t>Northwest Region</t>
   </si>
   <si>
+    <t>Cotton Belt (productivity weighted)</t>
+  </si>
+  <si>
+    <t>Southeast Region</t>
+  </si>
+  <si>
+    <t>South Atlantic-Gulf Basin</t>
+  </si>
+  <si>
     <t>Contiguous 48 States</t>
   </si>
   <si>
-    <t>Cotton Belt (productivity weighted)</t>
-  </si>
-  <si>
     <t>Primary Hard Red Winter Wheat Belt (area weighted)</t>
   </si>
   <si>
-    <t>Southeast Region</t>
-  </si>
-  <si>
-    <t>South Atlantic-Gulf Basin</t>
+    <t>Souris-Red-Rainy Basin</t>
+  </si>
+  <si>
+    <t>Spring Wheat Belt (productivity weighted)</t>
+  </si>
+  <si>
+    <t>NWS Southern Region</t>
+  </si>
+  <si>
+    <t>NWS Eastern Region</t>
   </si>
   <si>
     <t>Southern Plains and Gulf Coast</t>
   </si>
   <si>
-    <t>NWS Southern Region</t>
-  </si>
-  <si>
-    <t>Souris-Red-Rainy Basin</t>
-  </si>
-  <si>
-    <t>Spring Wheat Belt (productivity weighted)</t>
+    <t>Mid-Atlantic Basin</t>
+  </si>
+  <si>
+    <t>Arkansas-White-Red Basin</t>
   </si>
   <si>
     <t>Winter Wheat Belt (productivity weighted)</t>
   </si>
   <si>
-    <t>Arkansas-White-Red Basin</t>
-  </si>
-  <si>
     <t>Winter Wheat Belt (area weighted)</t>
   </si>
   <si>
-    <t>NWS Eastern Region</t>
-  </si>
-  <si>
     <t>South Region</t>
   </si>
   <si>
-    <t>Mid-Atlantic Basin</t>
+    <t>Northeast Region</t>
   </si>
   <si>
     <t>Texas Gulf Coast River Basin</t>
   </si>
   <si>
-    <t>Northeast Region</t>
-  </si>
-  <si>
     <t>NWS Central Region</t>
   </si>
   <si>
     <t>Mississippi River Basin &amp; Tributaties (N. of Memphis, TN)</t>
   </si>
   <si>
+    <t>Lower Mississippi River Basin</t>
+  </si>
+  <si>
     <t>New England Basin</t>
   </si>
   <si>
-    <t>Lower Mississippi River Basin</t>
+    <t>Tennessee River Basin</t>
+  </si>
+  <si>
+    <t>Soybean Belt (area weighted)</t>
+  </si>
+  <si>
+    <t>East North Central Region</t>
+  </si>
+  <si>
+    <t>Central Region</t>
+  </si>
+  <si>
+    <t>Ohio River Basin</t>
+  </si>
+  <si>
+    <t>Soybean Belt (productivity weighted)</t>
   </si>
   <si>
     <t>Upper Mississippi River Basin</t>
   </si>
   <si>
-    <t>Central Region</t>
-  </si>
-  <si>
-    <t>Tennessee River Basin</t>
-  </si>
-  <si>
-    <t>East North Central Region</t>
-  </si>
-  <si>
-    <t>Ohio River Basin</t>
-  </si>
-  <si>
-    <t>Soybean Belt (area weighted)</t>
-  </si>
-  <si>
     <t>Corn Belt (productivity weighted)</t>
   </si>
   <si>
-    <t>Soybean Belt (productivity weighted)</t>
+    <t>Great Lakes Basin</t>
+  </si>
+  <si>
+    <t>Primary Corn and Soybean Belt (area weighted)</t>
   </si>
   <si>
     <t>Corn Belt (area weighted)</t>
-  </si>
-  <si>
-    <t>Primary Corn and Soybean Belt (area weighted)</t>
-  </si>
-  <si>
-    <t>Great Lakes Basin</t>
   </si>
 </sst>
 </file>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.0242292717937432</v>
+        <v>-0.04111728312768175</v>
       </c>
       <c r="D2">
-        <v>1.361536372222681</v>
+        <v>2.152184992618269</v>
       </c>
       <c r="E2">
-        <v>-0.3433636466870638</v>
+        <v>-0.333270634045665</v>
       </c>
       <c r="F2">
-        <v>5.561734398160987E-05</v>
+        <v>9.430123383370697E-05</v>
       </c>
       <c r="G2">
-        <v>0.005812642727722151</v>
+        <v>0.0102021013910643</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-1.788268960963935</v>
+        <v>-3.193061813980358</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.0195179348926316</v>
+        <v>-0.0354926543127583</v>
       </c>
       <c r="D3">
-        <v>0.9925597278387577</v>
+        <v>1.668125553629886</v>
       </c>
       <c r="E3">
-        <v>-0.2832595488729124</v>
+        <v>-0.2947037933971848</v>
       </c>
       <c r="F3">
-        <v>0.000997872035987899</v>
+        <v>0.0006031547881164056</v>
       </c>
       <c r="G3">
-        <v>0.005795832686404338</v>
+        <v>0.0100937387789952</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-1.544771808203351</v>
+        <v>-2.945919507028692</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.01914644361351468</v>
+        <v>-0.03520480923531184</v>
       </c>
       <c r="D4">
-        <v>0.8453207156153437</v>
+        <v>1.633199435137044</v>
       </c>
       <c r="E4">
-        <v>-0.3049815496607023</v>
+        <v>-0.3082263854075711</v>
       </c>
       <c r="F4">
-        <v>0.0003769109845904483</v>
+        <v>0.0003237473086052675</v>
       </c>
       <c r="G4">
-        <v>0.005243765075453968</v>
+        <v>0.0095298036926331</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-1.643716954141565</v>
+        <v>-2.943425765453495</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,228 +669,228 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.01899561151987495</v>
+        <v>-0.03516737817673694</v>
       </c>
       <c r="D5">
-        <v>0.8529201855978288</v>
+        <v>1.624559085949035</v>
       </c>
       <c r="E5">
-        <v>-0.3091083706327353</v>
+        <v>-0.3150502793795322</v>
       </c>
       <c r="F5">
-        <v>0.0003105462961545191</v>
+        <v>0.0002338023968063934</v>
       </c>
       <c r="G5">
-        <v>0.00512582296567785</v>
+        <v>0.009291567191856467</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-1.616509311985916</v>
+        <v>-2.947200077026767</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.01816221964055587</v>
+        <v>-0.03214114858759574</v>
       </c>
       <c r="D6">
-        <v>0.845284792715469</v>
+        <v>1.481339880608512</v>
       </c>
       <c r="E6">
-        <v>-0.2993245206754295</v>
+        <v>-0.2613858524203089</v>
       </c>
       <c r="F6">
-        <v>0.0004892776564479321</v>
+        <v>0.002467127621015846</v>
       </c>
       <c r="G6">
-        <v>0.005077760681648033</v>
+        <v>0.01040975306785229</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-1.515803760556794</v>
+        <v>-2.697009435778934</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.01770115004066478</v>
+        <v>-0.03193480572960643</v>
       </c>
       <c r="D7">
-        <v>0.8732050883515357</v>
+        <v>1.504166762950126</v>
       </c>
       <c r="E7">
-        <v>-0.2647734759944448</v>
+        <v>-0.303711026177825</v>
       </c>
       <c r="F7">
-        <v>0.002154740689676274</v>
+        <v>0.0003998414569447658</v>
       </c>
       <c r="G7">
-        <v>0.005654214603724933</v>
+        <v>0.008786531522530169</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-1.427944416934885</v>
+        <v>-2.647357981898709</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.01677738128743328</v>
+        <v>-0.02890090901460052</v>
       </c>
       <c r="D8">
-        <v>0.871988702740869</v>
+        <v>1.27142011682393</v>
       </c>
       <c r="E8">
-        <v>-0.2892018089356432</v>
+        <v>-0.2635357900329363</v>
       </c>
       <c r="F8">
-        <v>0.0007703352438795139</v>
+        <v>0.002264457187312179</v>
       </c>
       <c r="G8">
-        <v>0.004870629595286091</v>
+        <v>0.009278330105987029</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-1.309070864625457</v>
+        <v>-2.485698055074139</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.01545061138232716</v>
+        <v>-0.02874178553970582</v>
       </c>
       <c r="D9">
-        <v>0.6701933280148187</v>
+        <v>1.213711149624495</v>
       </c>
       <c r="E9">
-        <v>-0.2918660848910308</v>
+        <v>-0.2438219605223619</v>
       </c>
       <c r="F9">
-        <v>0.0006846879266729982</v>
+        <v>0.004842833533217288</v>
       </c>
       <c r="G9">
-        <v>0.004440754927878409</v>
+        <v>0.01002675469026398</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.338386151687712</v>
+        <v>-2.522720970537262</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.01512685849999542</v>
+        <v>-0.02676889303648403</v>
       </c>
       <c r="D10">
-        <v>0.5422981165121548</v>
+        <v>1.240054303870596</v>
       </c>
       <c r="E10">
-        <v>-0.2292636454350772</v>
+        <v>-0.2491439574702416</v>
       </c>
       <c r="F10">
-        <v>0.008185911547748349</v>
+        <v>0.003966774212136206</v>
       </c>
       <c r="G10">
-        <v>0.00563270900956564</v>
+        <v>0.009126262648825437</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-1.424193488487249</v>
+        <v>-2.239901790872329</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.01056487050403861</v>
+        <v>-0.02276991610995078</v>
       </c>
       <c r="D11">
-        <v>1.239003507468845</v>
+        <v>1.625523332691444</v>
       </c>
       <c r="E11">
-        <v>-0.1420907439553266</v>
+        <v>-0.1931246087151366</v>
       </c>
       <c r="F11">
-        <v>0.1041138551910586</v>
+        <v>0.02650990564313749</v>
       </c>
       <c r="G11">
-        <v>0.0064550215508109</v>
+        <v>0.01014607981297265</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-0.1344296580561744</v>
+        <v>-1.334565761602157</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.01036907276560656</v>
+        <v>-0.02209735195801054</v>
       </c>
       <c r="D12">
-        <v>1.073722286411195</v>
+        <v>1.748128506322614</v>
       </c>
       <c r="E12">
-        <v>-0.1494860139776119</v>
+        <v>-0.1832983170225647</v>
       </c>
       <c r="F12">
-        <v>0.08712641065386849</v>
+        <v>0.03539888772411935</v>
       </c>
       <c r="G12">
-        <v>0.006015341112314004</v>
+        <v>0.01039414875957353</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-0.2742571731176586</v>
+        <v>-1.124527248218756</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +901,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.009555093606566747</v>
+        <v>-0.02166916213640651</v>
       </c>
       <c r="D13">
-        <v>0.4897442848889991</v>
+        <v>1.042746902882085</v>
       </c>
       <c r="E13">
-        <v>-0.1515493920118736</v>
+        <v>-0.1861985136023074</v>
       </c>
       <c r="F13">
-        <v>0.08280402418508151</v>
+        <v>0.0325458200363424</v>
       </c>
       <c r="G13">
-        <v>0.005465924634252097</v>
+        <v>0.01002841182613642</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-0.7524178839646779</v>
+        <v>-1.774244174850761</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,83 +930,83 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.00830573750660406</v>
+        <v>-0.01874265060954837</v>
       </c>
       <c r="D14">
-        <v>1.085046280249053</v>
+        <v>1.576846909300983</v>
       </c>
       <c r="E14">
-        <v>-0.1091636219617454</v>
+        <v>-0.1532499489898863</v>
       </c>
       <c r="F14">
-        <v>0.2127669818911371</v>
+        <v>0.07937229548615245</v>
       </c>
       <c r="G14">
-        <v>0.006633234777744247</v>
+        <v>0.01059981614303652</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>0.005300404390525815</v>
+        <v>-0.8596976699403047</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.00647406504529555</v>
+        <v>-0.01834930058708222</v>
       </c>
       <c r="D15">
-        <v>0.1063296332975709</v>
+        <v>1.565395596636498</v>
       </c>
       <c r="E15">
-        <v>-0.1473478036105982</v>
+        <v>-0.152193259081031</v>
       </c>
       <c r="F15">
-        <v>0.09179353959177503</v>
+        <v>0.08149097680561676</v>
       </c>
       <c r="G15">
-        <v>0.00381149379951017</v>
+        <v>0.0104511364867576</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.7352988225908506</v>
+        <v>-0.8200134796841902</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.006018843695620129</v>
+        <v>-0.01775037797429479</v>
       </c>
       <c r="D16">
-        <v>0.9204385253042102</v>
+        <v>0.614951408947943</v>
       </c>
       <c r="E16">
-        <v>-0.08520626192304384</v>
+        <v>-0.1835141072002174</v>
       </c>
       <c r="F16">
-        <v>0.3313479299554507</v>
+        <v>0.03517957528275933</v>
       </c>
       <c r="G16">
-        <v>0.006172876857522433</v>
+        <v>0.008339260417449833</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>0.1379888448735934</v>
+        <v>-1.692597727710379</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,518 +1017,518 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.005762927764834179</v>
+        <v>-0.01693782063626085</v>
       </c>
       <c r="D17">
-        <v>0.0740161022622029</v>
+        <v>0.5551537325887415</v>
       </c>
       <c r="E17">
-        <v>-0.132425653668514</v>
+        <v>-0.1748822372360749</v>
       </c>
       <c r="F17">
-        <v>0.1301124510592852</v>
+        <v>0.0448970906115275</v>
       </c>
       <c r="G17">
-        <v>0.003783184963858344</v>
+        <v>0.008363639212466316</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-0.6751645071662403</v>
+        <v>-1.646762950125169</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.003575762808345131</v>
+        <v>-0.016118123509458</v>
       </c>
       <c r="D18">
-        <v>0.3870015130257765</v>
+        <v>0.6801297901020604</v>
       </c>
       <c r="E18">
-        <v>-0.05744731586972401</v>
+        <v>-0.1477548333122258</v>
       </c>
       <c r="F18">
-        <v>0.5129298389809755</v>
+        <v>0.09089012647408326</v>
       </c>
       <c r="G18">
-        <v>0.005450162758518218</v>
+        <v>0.009462544731114551</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-0.07784765205909056</v>
+        <v>-1.415226266127479</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.003036299710303177</v>
+        <v>-0.01476564606200655</v>
       </c>
       <c r="D19">
-        <v>0.03749254490935611</v>
+        <v>0.5900500673984211</v>
       </c>
       <c r="E19">
-        <v>-0.05539405551895612</v>
+        <v>-0.1521850971151991</v>
       </c>
       <c r="F19">
-        <v>0.5281316188901691</v>
+        <v>0.08150751648878281</v>
       </c>
       <c r="G19">
-        <v>0.004800013502279487</v>
+        <v>0.008410470697014213</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-0.3572264174300569</v>
+        <v>-1.32948392066243</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.001862715588538815</v>
+        <v>-0.01455033847338874</v>
       </c>
       <c r="D20">
-        <v>0.3642717440143785</v>
+        <v>0.5842014249951861</v>
       </c>
       <c r="E20">
-        <v>-0.02943782181859346</v>
+        <v>-0.1503718553996254</v>
       </c>
       <c r="F20">
-        <v>0.7375718099275663</v>
+        <v>0.08524919066886252</v>
       </c>
       <c r="G20">
-        <v>0.005547290919924566</v>
+        <v>0.008390124989110107</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>0.1221187175043325</v>
+        <v>-1.307342576545349</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.001810089307316344</v>
+        <v>-0.01418980382862532</v>
       </c>
       <c r="D21">
-        <v>-0.02161000155887499</v>
+        <v>0.8176881699723988</v>
       </c>
       <c r="E21">
-        <v>-0.04107575023877021</v>
+        <v>-0.1309174200834989</v>
       </c>
       <c r="F21">
-        <v>0.6400468380403856</v>
+        <v>0.1345837658790083</v>
       </c>
       <c r="G21">
-        <v>0.003861678713927509</v>
+        <v>0.009424389925037989</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.2569216115099997</v>
+        <v>-1.026986327748893</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.001437618335191992</v>
+        <v>-0.01312143862299842</v>
       </c>
       <c r="D22">
-        <v>-0.04084757411533846</v>
+        <v>0.8825499711149626</v>
       </c>
       <c r="E22">
-        <v>-0.03297503880781006</v>
+        <v>-0.1166495105453306</v>
       </c>
       <c r="F22">
-        <v>0.7073978809917814</v>
+        <v>0.1828581989358968</v>
       </c>
       <c r="G22">
-        <v>0.003821645222086447</v>
+        <v>0.009798324612286118</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-0.2277379576902974</v>
+        <v>-0.8232370498748317</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23">
-        <v>2.540888728063946E-05</v>
+        <v>-0.01200629051928879</v>
       </c>
       <c r="D23">
-        <v>-0.1938948859728756</v>
+        <v>1.319768277809872</v>
       </c>
       <c r="E23">
-        <v>0.0003965764441475179</v>
+        <v>-0.1123226544889668</v>
       </c>
       <c r="F23">
-        <v>0.9963991749479508</v>
+        <v>0.1997455373082697</v>
       </c>
       <c r="G23">
-        <v>0.005619362150124373</v>
+        <v>0.009315641623505211</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.1905917306263925</v>
+        <v>-0.2410494896976703</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>0.001044903289790641</v>
+        <v>-0.0114221254450024</v>
       </c>
       <c r="D24">
-        <v>-0.190557105260745</v>
+        <v>1.201473650426857</v>
       </c>
       <c r="E24">
-        <v>0.01703468093081781</v>
+        <v>-0.1000551481479761</v>
       </c>
       <c r="F24">
-        <v>0.8462806715824522</v>
+        <v>0.2536704118578745</v>
       </c>
       <c r="G24">
-        <v>0.005379072477057753</v>
+        <v>0.009962102076821095</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.0547196775879617</v>
+        <v>-0.2834026574234547</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>0.00152047712862271</v>
+        <v>-0.01111277607430121</v>
       </c>
       <c r="D25">
-        <v>0.6362840132779474</v>
+        <v>0.3604340458309263</v>
       </c>
       <c r="E25">
-        <v>0.02598619013266422</v>
+        <v>-0.1002863383312097</v>
       </c>
       <c r="F25">
-        <v>0.7674065782891644</v>
+        <v>0.2525695346931657</v>
       </c>
       <c r="G25">
-        <v>0.005130018351700557</v>
+        <v>0.00966972515868691</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>0.8339460399988997</v>
+        <v>-1.08422684382823</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26">
-        <v>0.00190454775342124</v>
+        <v>-0.01086160956316936</v>
       </c>
       <c r="D26">
-        <v>0.5085056669692716</v>
+        <v>0.6409944155594071</v>
       </c>
       <c r="E26">
-        <v>0.02997957376624883</v>
+        <v>-0.1149466535333391</v>
       </c>
       <c r="F26">
-        <v>0.732923086705537</v>
+        <v>0.1893749576310764</v>
       </c>
       <c r="G26">
-        <v>0.005569285501922459</v>
+        <v>0.008232617683450377</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>0.7560968749140327</v>
+        <v>-0.7710148276526095</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <v>0.002108647594782777</v>
+        <v>-0.01074279873794605</v>
       </c>
       <c r="D27">
-        <v>0.2316743464187138</v>
+        <v>0.2346593491238206</v>
       </c>
       <c r="E27">
-        <v>0.03340508239261034</v>
+        <v>-0.09459117424017852</v>
       </c>
       <c r="F27">
-        <v>0.7037591199110842</v>
+        <v>0.28065262513802</v>
       </c>
       <c r="G27">
-        <v>0.005533212273940767</v>
+        <v>0.009916158944663573</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>0.5057985337404749</v>
+        <v>-1.161904486809166</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28">
-        <v>0.002439939577721208</v>
+        <v>-0.008968892048961372</v>
       </c>
       <c r="D28">
-        <v>0.04202768378678248</v>
+        <v>0.4190466653828873</v>
       </c>
       <c r="E28">
-        <v>0.04105844441065122</v>
+        <v>-0.09541306962247023</v>
       </c>
       <c r="F28">
-        <v>0.6401878815763661</v>
+        <v>0.2764753341809382</v>
       </c>
       <c r="G28">
-        <v>0.005207610926418394</v>
+        <v>0.008206790857740866</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>0.3592198288905396</v>
+        <v>-0.7469093009820911</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>0.002857739744048238</v>
+        <v>-0.008864252173784237</v>
       </c>
       <c r="D29">
-        <v>0.2391449845487973</v>
+        <v>0.5989905642210669</v>
       </c>
       <c r="E29">
-        <v>0.04453909216620151</v>
+        <v>-0.0813703829927914</v>
       </c>
       <c r="F29">
-        <v>0.6120846955151322</v>
+        <v>0.3536555971947979</v>
       </c>
       <c r="G29">
-        <v>0.005621839576934341</v>
+        <v>0.009522731148012709</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>0.6106511512750683</v>
+        <v>-0.553362218370884</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>0.002931696514538803</v>
+        <v>-0.007303200067151539</v>
       </c>
       <c r="D30">
-        <v>-0.052839206624302</v>
+        <v>0.5755858527504973</v>
       </c>
       <c r="E30">
-        <v>0.07145240488755111</v>
+        <v>-0.06681667839469289</v>
       </c>
       <c r="F30">
-        <v>0.4155538888860361</v>
+        <v>0.4465286735177345</v>
       </c>
       <c r="G30">
-        <v>0.003589376464119453</v>
+        <v>0.009565001055725322</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>0.3282813402657424</v>
+        <v>-0.3738301559792027</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31">
-        <v>0.003935481688861243</v>
+        <v>-0.007006447535390342</v>
       </c>
       <c r="D31">
-        <v>-0.3111730855639004</v>
+        <v>0.591760575133192</v>
       </c>
       <c r="E31">
-        <v>0.06431732717491406</v>
+        <v>-0.06339042792373104</v>
       </c>
       <c r="F31">
-        <v>0.4637532562272021</v>
+        <v>0.4702328538852097</v>
       </c>
       <c r="G31">
-        <v>0.005355476174432985</v>
+        <v>0.009674492315024669</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>0.2004395339880612</v>
+        <v>-0.3190776044675525</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32">
-        <v>0.004271410584408853</v>
+        <v>-0.006418721454423364</v>
       </c>
       <c r="D32">
-        <v>-0.2379640450056396</v>
+        <v>0.1261437832980296</v>
       </c>
       <c r="E32">
-        <v>0.1043174944241128</v>
+        <v>-0.05747180130174274</v>
       </c>
       <c r="F32">
-        <v>0.233901701963495</v>
+        <v>0.5127499249559127</v>
       </c>
       <c r="G32">
-        <v>0.003571630459064229</v>
+        <v>0.00977920652551458</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.3173193309675112</v>
+        <v>-0.7082900057770077</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>0.005347780366497873</v>
+        <v>-0.005724463404879348</v>
       </c>
       <c r="D33">
-        <v>-0.5161684364483327</v>
+        <v>0.2182799922973233</v>
       </c>
       <c r="E33">
-        <v>0.08759124272052549</v>
+        <v>-0.06139690056706821</v>
       </c>
       <c r="F33">
-        <v>0.3179418731676054</v>
+        <v>0.4843347795269108</v>
       </c>
       <c r="G33">
-        <v>0.005334193572658925</v>
+        <v>0.008161999410810049</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>0.1790430111963908</v>
+        <v>-0.5259002503369919</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
       <c r="C34">
-        <v>0.007110822472347606</v>
+        <v>-0.00489731838224039</v>
       </c>
       <c r="D34">
-        <v>-0.399862617259498</v>
+        <v>-0.1439089800372297</v>
       </c>
       <c r="E34">
-        <v>0.1722237899985017</v>
+        <v>-0.04372949492794493</v>
       </c>
       <c r="F34">
-        <v>0.0483065649744502</v>
+        <v>0.6185733080205327</v>
       </c>
       <c r="G34">
-        <v>0.003567112068191183</v>
+        <v>0.009812881632502893</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>0.5245443041456909</v>
+        <v>-0.7805603697284804</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,25 +1539,25 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>0.007821855287019933</v>
+        <v>-0.004456768727132679</v>
       </c>
       <c r="D35">
-        <v>-0.01924112128964822</v>
+        <v>0.5064394377046025</v>
       </c>
       <c r="E35">
-        <v>0.1363867005446065</v>
+        <v>-0.04294545397437286</v>
       </c>
       <c r="F35">
-        <v>0.1189121391352015</v>
+        <v>0.6248852444927793</v>
       </c>
       <c r="G35">
-        <v>0.004982976162412835</v>
+        <v>0.009093485253326818</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>0.9976000660229432</v>
+        <v>-0.07294049682264581</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,199 +1568,199 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>0.008393815780470895</v>
+        <v>-0.003423707456289775</v>
       </c>
       <c r="D36">
-        <v>0.07249366821637182</v>
+        <v>0.5321549521792155</v>
       </c>
       <c r="E36">
-        <v>0.1362318541479565</v>
+        <v>-0.03264974613172606</v>
       </c>
       <c r="F36">
-        <v>0.1193354753295819</v>
+        <v>0.7101547054189534</v>
       </c>
       <c r="G36">
-        <v>0.005353541358067393</v>
+        <v>0.009192075017750663</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>1.163689719677588</v>
+        <v>0.08707298286154475</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
       <c r="C37">
-        <v>0.008399214919492217</v>
+        <v>-0.003265620880178941</v>
       </c>
       <c r="D37">
-        <v>-0.4820385133834008</v>
+        <v>-0.1042002695936837</v>
       </c>
       <c r="E37">
-        <v>0.2094325350421893</v>
+        <v>-0.03384657014046923</v>
       </c>
       <c r="F37">
-        <v>0.01594805763069651</v>
+        <v>0.7000304878992039</v>
       </c>
       <c r="G37">
-        <v>0.00343940375285565</v>
+        <v>0.008457276273614908</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.6098594261505874</v>
+        <v>-0.5287309840169461</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>45</v>
       </c>
       <c r="C38">
-        <v>0.008756455047616228</v>
+        <v>-0.003253436825707188</v>
       </c>
       <c r="D38">
-        <v>-0.6796718568035728</v>
+        <v>0.0788894024006675</v>
       </c>
       <c r="E38">
-        <v>0.2021982097579776</v>
+        <v>-0.03534695764843575</v>
       </c>
       <c r="F38">
-        <v>0.0200690315266599</v>
+        <v>0.6874125905292188</v>
       </c>
       <c r="G38">
-        <v>0.003719759674662339</v>
+        <v>0.008067652574073554</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>0.4586672993865369</v>
+        <v>-0.3440573849412669</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
       </c>
       <c r="C39">
-        <v>0.01115673021374928</v>
+        <v>-0.00245753701975539</v>
       </c>
       <c r="D39">
-        <v>-0.1902526477951089</v>
+        <v>0.2128266255857243</v>
       </c>
       <c r="E39">
-        <v>0.214437253747496</v>
+        <v>-0.02579645966558611</v>
       </c>
       <c r="F39">
-        <v>0.01354699123863075</v>
+        <v>0.7690569232918916</v>
       </c>
       <c r="G39">
-        <v>0.004457003743779231</v>
+        <v>0.008352639452420233</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>1.260122279992297</v>
+        <v>-0.1066531869824763</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.01132875496670991</v>
+        <v>0.0006460294182997867</v>
       </c>
       <c r="D40">
-        <v>-0.5327133182947743</v>
+        <v>0.1900735605622951</v>
       </c>
       <c r="E40">
-        <v>0.2257851192089127</v>
+        <v>0.006408425665928393</v>
       </c>
       <c r="F40">
-        <v>0.009238357153026934</v>
+        <v>0.9418636781165285</v>
       </c>
       <c r="G40">
-        <v>0.004286996424710866</v>
+        <v>0.008841385962717344</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.9400248273775138</v>
+        <v>0.2740573849412674</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.01185741604823061</v>
+        <v>0.001063998380462854</v>
       </c>
       <c r="D41">
-        <v>-0.6225020219526289</v>
+        <v>0.1004169715642851</v>
       </c>
       <c r="E41">
-        <v>0.2522684218117975</v>
+        <v>0.01110318254212832</v>
       </c>
       <c r="F41">
-        <v>0.003521417184292506</v>
+        <v>0.8994497826074022</v>
       </c>
       <c r="G41">
-        <v>0.003989119695662025</v>
+        <v>0.008404174071393001</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>0.9189620643173508</v>
+        <v>0.2387367610244561</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.01186726475270669</v>
+        <v>0.00125957526650768</v>
       </c>
       <c r="D42">
-        <v>-0.3374674653608795</v>
+        <v>-0.1428146864368704</v>
       </c>
       <c r="E42">
-        <v>0.2379675286947799</v>
+        <v>0.01300134858355682</v>
       </c>
       <c r="F42">
-        <v>0.006002933199257258</v>
+        <v>0.882374618843337</v>
       </c>
       <c r="G42">
-        <v>0.004248177166548183</v>
+        <v>0.008496251055096028</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>1.205276952490991</v>
+        <v>0.02093009820912803</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1771,141 +1771,141 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.01187033651245091</v>
+        <v>0.00127711366879478</v>
       </c>
       <c r="D43">
-        <v>-0.570703717458484</v>
+        <v>-0.1273631170164966</v>
       </c>
       <c r="E43">
-        <v>0.2510771454764286</v>
+        <v>0.01354668431468313</v>
       </c>
       <c r="F43">
-        <v>0.003685621984393542</v>
+        <v>0.8774786124672767</v>
       </c>
       <c r="G43">
-        <v>0.004013698624020564</v>
+        <v>0.008267705790818673</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.9724400291601337</v>
+        <v>0.03866165992682474</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.01222732609197081</v>
+        <v>0.001531937963827049</v>
       </c>
       <c r="D44">
-        <v>-0.2848038293306927</v>
+        <v>0.06912651646447122</v>
       </c>
       <c r="E44">
-        <v>0.2193230963876298</v>
+        <v>0.01524953984213023</v>
       </c>
       <c r="F44">
-        <v>0.01151376851537947</v>
+        <v>0.8622210484901547</v>
       </c>
       <c r="G44">
-        <v>0.00477057266593141</v>
+        <v>0.008809723147044599</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>1.304748562625513</v>
+        <v>0.2682784517619876</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.01259091034775611</v>
+        <v>0.001654673204066622</v>
       </c>
       <c r="D45">
-        <v>-0.2764693176712246</v>
+        <v>0.1544360998780407</v>
       </c>
       <c r="E45">
-        <v>0.2145912692164529</v>
+        <v>0.01691062635014135</v>
       </c>
       <c r="F45">
-        <v>0.01347840132082122</v>
+        <v>0.8473864835681691</v>
       </c>
       <c r="G45">
-        <v>0.005026160431260993</v>
+        <v>0.008580621748813506</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>1.360349027537069</v>
+        <v>0.3695436164067016</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.01260063864500607</v>
+        <v>0.001986808672423925</v>
       </c>
       <c r="D46">
-        <v>-0.3572018238838</v>
+        <v>0.10803491880095</v>
       </c>
       <c r="E46">
-        <v>0.2282365454499782</v>
+        <v>0.0194703191124432</v>
       </c>
       <c r="F46">
-        <v>0.00848504202964943</v>
+        <v>0.8246328266021964</v>
       </c>
       <c r="G46">
-        <v>0.004714317285279634</v>
+        <v>0.008948061630305976</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>1.280881199966989</v>
+        <v>0.3663200462160603</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.01309879099012548</v>
+        <v>0.002156893648748073</v>
       </c>
       <c r="D47">
-        <v>-0.2239657689380398</v>
+        <v>-0.111127928621863</v>
       </c>
       <c r="E47">
-        <v>0.2217557480362156</v>
+        <v>0.02406719518175246</v>
       </c>
       <c r="F47">
-        <v>0.01060516015413699</v>
+        <v>0.784145527287415</v>
       </c>
       <c r="G47">
-        <v>0.00505166807163727</v>
+        <v>0.007857886667540061</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>1.478877059778273</v>
+        <v>0.1692682457153865</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1916,54 +1916,54 @@
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.01332522598397816</v>
+        <v>0.002302158230754418</v>
       </c>
       <c r="D48">
-        <v>-0.4074404463884536</v>
+        <v>0.01191719622568843</v>
       </c>
       <c r="E48">
-        <v>0.2499744933476447</v>
+        <v>0.0231784903847785</v>
       </c>
       <c r="F48">
-        <v>0.003843708608584239</v>
+        <v>0.7919315821105954</v>
       </c>
       <c r="G48">
-        <v>0.00452684685133213</v>
+        <v>0.00870886693422857</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>1.324838931528707</v>
+        <v>0.3111977662237628</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.01512443215684118</v>
+        <v>0.003268334592424712</v>
       </c>
       <c r="D49">
-        <v>-0.7050859077696172</v>
+        <v>0.06276526092817261</v>
       </c>
       <c r="E49">
-        <v>0.3421226967954395</v>
+        <v>0.03235106579144525</v>
       </c>
       <c r="F49">
-        <v>5.940604506866973E-05</v>
+        <v>0.7126892997860301</v>
       </c>
       <c r="G49">
-        <v>0.00364329281599949</v>
+        <v>0.008856025494381504</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>1.261090272619736</v>
+        <v>0.4876487579433852</v>
       </c>
     </row>
   </sheetData>

--- a/output/palmer_drought_trendlines/region/Half-Decade.xlsx
+++ b/output/palmer_drought_trendlines/region/Half-Decade.xlsx
@@ -73,12 +73,12 @@
     <t>Spring Wheat Belt (area weighted)</t>
   </si>
   <si>
+    <t>Cotton Belt (area weighted)</t>
+  </si>
+  <si>
     <t>West North Central Region</t>
   </si>
   <si>
-    <t>Cotton Belt (area weighted)</t>
-  </si>
-  <si>
     <t>Missouri River Basin</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>Souris-Red-Rainy Basin</t>
   </si>
   <si>
+    <t>NWS Southern Region</t>
+  </si>
+  <si>
     <t>Spring Wheat Belt (productivity weighted)</t>
   </si>
   <si>
-    <t>NWS Southern Region</t>
+    <t>Southern Plains and Gulf Coast</t>
   </si>
   <si>
     <t>NWS Eastern Region</t>
   </si>
   <si>
-    <t>Southern Plains and Gulf Coast</t>
+    <t>Arkansas-White-Red Basin</t>
   </si>
   <si>
     <t>Mid-Atlantic Basin</t>
   </si>
   <si>
-    <t>Arkansas-White-Red Basin</t>
-  </si>
-  <si>
     <t>Winter Wheat Belt (productivity weighted)</t>
   </si>
   <si>
@@ -178,10 +178,10 @@
     <t>Corn Belt (productivity weighted)</t>
   </si>
   <si>
+    <t>Primary Corn and Soybean Belt (area weighted)</t>
+  </si>
+  <si>
     <t>Great Lakes Basin</t>
-  </si>
-  <si>
-    <t>Primary Corn and Soybean Belt (area weighted)</t>
   </si>
   <si>
     <t>Corn Belt (area weighted)</t>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.04111728312768175</v>
+        <v>-0.03063952460659568</v>
       </c>
       <c r="D2">
-        <v>2.152184992618269</v>
+        <v>1.715611720906349</v>
       </c>
       <c r="E2">
-        <v>-0.333270634045665</v>
+        <v>-0.350707902076795</v>
       </c>
       <c r="F2">
-        <v>9.430123383370697E-05</v>
+        <v>3.744067189077215E-05</v>
       </c>
       <c r="G2">
-        <v>0.0102021013910643</v>
+        <v>0.007175721488532544</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-3.193061813980358</v>
+        <v>-2.267526477951089</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.0354926543127583</v>
+        <v>-0.0250079633826601</v>
       </c>
       <c r="D3">
-        <v>1.668125553629886</v>
+        <v>1.231263431542461</v>
       </c>
       <c r="E3">
-        <v>-0.2947037933971848</v>
+        <v>-0.2996199455462846</v>
       </c>
       <c r="F3">
-        <v>0.0006031547881164056</v>
+        <v>0.000482718664851885</v>
       </c>
       <c r="G3">
-        <v>0.0100937387789952</v>
+        <v>0.006984108806159801</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-2.945919507028692</v>
+        <v>-2.019771808203351</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.03520480923531184</v>
+        <v>-0.02442491322144702</v>
       </c>
       <c r="D4">
-        <v>1.633199435137044</v>
+        <v>1.18403710122601</v>
       </c>
       <c r="E4">
-        <v>-0.3082263854075711</v>
+        <v>-0.3155830481794448</v>
       </c>
       <c r="F4">
-        <v>0.0003237473086052675</v>
+        <v>0.0002278607077738074</v>
       </c>
       <c r="G4">
-        <v>0.0095298036926331</v>
+        <v>0.006441206163782562</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-2.943425765453495</v>
+        <v>-1.991201617562103</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,25 +669,25 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.03516737817673694</v>
+        <v>-0.02407090215131811</v>
       </c>
       <c r="D5">
-        <v>1.624559085949035</v>
+        <v>1.16220591822325</v>
       </c>
       <c r="E5">
-        <v>-0.3150502793795322</v>
+        <v>-0.3117786814324019</v>
       </c>
       <c r="F5">
-        <v>0.0002338023968063934</v>
+        <v>0.0002735543419948047</v>
       </c>
       <c r="G5">
-        <v>0.009291567191856467</v>
+        <v>0.006433815761243405</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-2.947200077026767</v>
+        <v>-1.967011361448104</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -698,25 +698,25 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.03214114858759574</v>
+        <v>-0.02157095794634789</v>
       </c>
       <c r="D6">
-        <v>1.481339880608512</v>
+        <v>1.040915270556519</v>
       </c>
       <c r="E6">
-        <v>-0.2613858524203089</v>
+        <v>-0.2456932581801399</v>
       </c>
       <c r="F6">
-        <v>0.002467127621015846</v>
+        <v>0.004516821551543975</v>
       </c>
       <c r="G6">
-        <v>0.01040975306785229</v>
+        <v>0.007464213757183916</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-2.697009435778934</v>
+        <v>-1.763309262468708</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -727,25 +727,25 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.03193480572960643</v>
+        <v>-0.02075976240205011</v>
       </c>
       <c r="D7">
-        <v>1.504166762950126</v>
+        <v>1.038539957635279</v>
       </c>
       <c r="E7">
-        <v>-0.303711026177825</v>
+        <v>-0.303703610762576</v>
       </c>
       <c r="F7">
-        <v>0.0003998414569447658</v>
+        <v>0.0003999789927631374</v>
       </c>
       <c r="G7">
-        <v>0.008786531522530169</v>
+        <v>0.005711987559558846</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-2.647357981898709</v>
+        <v>-1.660229154631235</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -756,25 +756,25 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.02890090901460052</v>
+        <v>-0.01806613142938966</v>
       </c>
       <c r="D8">
-        <v>1.27142011682393</v>
+        <v>0.8199710507734771</v>
       </c>
       <c r="E8">
-        <v>-0.2635357900329363</v>
+        <v>-0.254188159908864</v>
       </c>
       <c r="F8">
-        <v>0.002264457187312179</v>
+        <v>0.003270608152506843</v>
       </c>
       <c r="G8">
-        <v>0.009278330105987029</v>
+        <v>0.006028845536713266</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-2.485698055074139</v>
+        <v>-1.528626035047179</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -785,25 +785,25 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.02874178553970582</v>
+        <v>-0.01778569079678266</v>
       </c>
       <c r="D9">
-        <v>1.213711149624495</v>
+        <v>0.7572072020026964</v>
       </c>
       <c r="E9">
-        <v>-0.2438219605223619</v>
+        <v>-0.2103941787102173</v>
       </c>
       <c r="F9">
-        <v>0.004842833533217288</v>
+        <v>0.01545990353370884</v>
       </c>
       <c r="G9">
-        <v>0.01002675469026398</v>
+        <v>0.007248262717735568</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-2.522720970537262</v>
+        <v>-1.554932601579049</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,25 +814,25 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.02676889303648403</v>
+        <v>-0.01579777807403458</v>
       </c>
       <c r="D10">
-        <v>1.240054303870596</v>
+        <v>0.782924513768535</v>
       </c>
       <c r="E10">
-        <v>-0.2491439574702416</v>
+        <v>-0.2287150082336353</v>
       </c>
       <c r="F10">
-        <v>0.003966774212136206</v>
+        <v>0.008344514145621224</v>
       </c>
       <c r="G10">
-        <v>0.009126262648825437</v>
+        <v>0.005897428583853349</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-2.239901790872329</v>
+        <v>-1.27078663585596</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,83 +843,83 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.02276991610995078</v>
+        <v>-0.01174103107240023</v>
       </c>
       <c r="D11">
-        <v>1.625523332691444</v>
+        <v>1.165986456126838</v>
       </c>
       <c r="E11">
-        <v>-0.1931246087151366</v>
+        <v>-0.1401514340519322</v>
       </c>
       <c r="F11">
-        <v>0.02650990564313749</v>
+        <v>0.1089735900680674</v>
       </c>
       <c r="G11">
-        <v>0.01014607981297265</v>
+        <v>0.00727493755579613</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-1.334565761602157</v>
+        <v>-0.3603475832851919</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.02209735195801054</v>
+        <v>-0.01118735971006335</v>
       </c>
       <c r="D12">
-        <v>1.748128506322614</v>
+        <v>0.6060051351177869</v>
       </c>
       <c r="E12">
-        <v>-0.1832983170225647</v>
+        <v>-0.1453852509969357</v>
       </c>
       <c r="F12">
-        <v>0.03539888772411935</v>
+        <v>0.09624999547311541</v>
       </c>
       <c r="G12">
-        <v>0.01039414875957353</v>
+        <v>0.006677233454085394</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-1.124527248218756</v>
+        <v>-0.8483516271904488</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.02166916213640651</v>
+        <v>-0.01104824739417461</v>
       </c>
       <c r="D13">
-        <v>1.042746902882085</v>
+        <v>1.287749149496117</v>
       </c>
       <c r="E13">
-        <v>-0.1861985136023074</v>
+        <v>-0.1264734388862798</v>
       </c>
       <c r="F13">
-        <v>0.0325458200363424</v>
+        <v>0.1484415408865201</v>
       </c>
       <c r="G13">
-        <v>0.01002841182613642</v>
+        <v>0.007600128274911064</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-1.774244174850761</v>
+        <v>-0.1485230117465821</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,25 +930,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.01874265060954837</v>
+        <v>-0.007769224844094866</v>
       </c>
       <c r="D14">
-        <v>1.576846909300983</v>
+        <v>1.11962083574042</v>
       </c>
       <c r="E14">
-        <v>-0.1532499489898863</v>
+        <v>-0.08736106883190932</v>
       </c>
       <c r="F14">
-        <v>0.07937229548615245</v>
+        <v>0.3192201542306497</v>
       </c>
       <c r="G14">
-        <v>0.01059981614303652</v>
+        <v>0.007770061577606098</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-0.8596976699403047</v>
+        <v>0.1096216060080877</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -959,25 +959,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.01834930058708222</v>
+        <v>-0.007382229529889841</v>
       </c>
       <c r="D15">
-        <v>1.565395596636498</v>
+        <v>1.108434302586816</v>
       </c>
       <c r="E15">
-        <v>-0.152193259081031</v>
+        <v>-0.08540216527513418</v>
       </c>
       <c r="F15">
-        <v>0.08149097680561676</v>
+        <v>0.3302333245326238</v>
       </c>
       <c r="G15">
-        <v>0.0104511364867576</v>
+        <v>0.007553659646783517</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.8200134796841902</v>
+        <v>0.1487444637011363</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -988,25 +988,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.01775037797429479</v>
+        <v>-0.006623861509823383</v>
       </c>
       <c r="D16">
-        <v>0.614951408947943</v>
+        <v>0.1513465562616344</v>
       </c>
       <c r="E16">
-        <v>-0.1835141072002174</v>
+        <v>-0.1234563658171055</v>
       </c>
       <c r="F16">
-        <v>0.03517957528275933</v>
+        <v>0.1584463390885356</v>
       </c>
       <c r="G16">
-        <v>0.008339260417449833</v>
+        <v>0.004669721216274888</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-1.692597727710379</v>
+        <v>-0.7097554400154054</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,25 +1017,25 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.01693782063626085</v>
+        <v>-0.005841922311593022</v>
       </c>
       <c r="D17">
-        <v>0.5551537325887415</v>
+        <v>0.09282463572758209</v>
       </c>
       <c r="E17">
-        <v>-0.1748822372360749</v>
+        <v>-0.1094217400785307</v>
       </c>
       <c r="F17">
-        <v>0.0448970906115275</v>
+        <v>0.2116808316094213</v>
       </c>
       <c r="G17">
-        <v>0.008363639212466316</v>
+        <v>0.004654412442225635</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-1.646762950125169</v>
+        <v>-0.6666252647795108</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1046,25 +1046,25 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.016118123509458</v>
+        <v>-0.005534068050185904</v>
       </c>
       <c r="D18">
-        <v>0.6801297901020604</v>
+        <v>0.2391274792990566</v>
       </c>
       <c r="E18">
-        <v>-0.1477548333122258</v>
+        <v>-0.0830431220690233</v>
       </c>
       <c r="F18">
-        <v>0.09089012647408326</v>
+        <v>0.3438148046194536</v>
       </c>
       <c r="G18">
-        <v>0.009462544731114551</v>
+        <v>0.005824605032917552</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-1.415226266127479</v>
+        <v>-0.4803013672251109</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1075,25 +1075,25 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.01476564606200655</v>
+        <v>-0.003618910071249759</v>
       </c>
       <c r="D19">
-        <v>0.5900500673984211</v>
+        <v>0.1256027344502214</v>
       </c>
       <c r="E19">
-        <v>-0.1521850971151991</v>
+        <v>-0.06698779971229464</v>
       </c>
       <c r="F19">
-        <v>0.08150751648878281</v>
+        <v>0.4453626852585783</v>
       </c>
       <c r="G19">
-        <v>0.008410470697014213</v>
+        <v>0.004727524519596086</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-1.32948392066243</v>
+        <v>-0.3448555748122473</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1104,25 +1104,25 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.01455033847338874</v>
+        <v>-0.003358541824053091</v>
       </c>
       <c r="D20">
-        <v>0.5842014249951861</v>
+        <v>0.1178765646062008</v>
       </c>
       <c r="E20">
-        <v>-0.1503718553996254</v>
+        <v>-0.06185512454042712</v>
       </c>
       <c r="F20">
-        <v>0.08524919066886252</v>
+        <v>0.4810734486869322</v>
       </c>
       <c r="G20">
-        <v>0.008390124989110107</v>
+        <v>0.0047530347349147</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-1.307342576545349</v>
+        <v>-0.318733872520701</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1133,25 +1133,25 @@
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.01418980382862532</v>
+        <v>-0.003317475694598746</v>
       </c>
       <c r="D21">
-        <v>0.8176881699723988</v>
+        <v>0.3646744977212915</v>
       </c>
       <c r="E21">
-        <v>-0.1309174200834989</v>
+        <v>-0.04849504796880764</v>
       </c>
       <c r="F21">
-        <v>0.1345837658790083</v>
+        <v>0.5808172148757991</v>
       </c>
       <c r="G21">
-        <v>0.009424389925037989</v>
+        <v>0.005992767082653672</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-1.026986327748893</v>
+        <v>-0.06659734257654543</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1162,25 +1162,25 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.01312143862299842</v>
+        <v>-0.002059046941889228</v>
       </c>
       <c r="D22">
-        <v>0.8825499711149626</v>
+        <v>0.4216169844020795</v>
       </c>
       <c r="E22">
-        <v>-0.1166495105453306</v>
+        <v>-0.02686849710242522</v>
       </c>
       <c r="F22">
-        <v>0.1828581989358968</v>
+        <v>0.7597457487160444</v>
       </c>
       <c r="G22">
-        <v>0.009798324612286118</v>
+        <v>0.006718841223073863</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-0.8232370498748317</v>
+        <v>0.1539408819564799</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,199 +1191,199 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>-0.01200629051928879</v>
+        <v>-0.0006573592656781529</v>
       </c>
       <c r="D23">
-        <v>1.319768277809872</v>
+        <v>0.8468961422427624</v>
       </c>
       <c r="E23">
-        <v>-0.1123226544889668</v>
+        <v>-0.009295642640728161</v>
       </c>
       <c r="F23">
-        <v>0.1997455373082697</v>
+        <v>0.9157527025140926</v>
       </c>
       <c r="G23">
-        <v>0.009315641623505211</v>
+        <v>0.006202016665901177</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.2410494896976703</v>
+        <v>0.7614394377046025</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>-0.0114221254450024</v>
+        <v>-0.0003357685641914401</v>
       </c>
       <c r="D24">
-        <v>1.201473650426857</v>
+        <v>-0.08860793375698067</v>
       </c>
       <c r="E24">
-        <v>-0.1000551481479761</v>
+        <v>-0.004685590204086268</v>
       </c>
       <c r="F24">
-        <v>0.2536704118578745</v>
+        <v>0.957475668571576</v>
       </c>
       <c r="G24">
-        <v>0.009962102076821095</v>
+        <v>0.006284913240366198</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.2834026574234547</v>
+        <v>-0.1322578471018679</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>-0.01111277607430121</v>
+        <v>-9.919072518725564E-05</v>
       </c>
       <c r="D25">
-        <v>0.3604340458309263</v>
+        <v>0.7296847037678925</v>
       </c>
       <c r="E25">
-        <v>-0.1002863383312097</v>
+        <v>-0.001222260277761722</v>
       </c>
       <c r="F25">
-        <v>0.2525695346931657</v>
+        <v>0.9889024676138916</v>
       </c>
       <c r="G25">
-        <v>0.00966972515868691</v>
+        <v>0.007117629327126168</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>-1.08422684382823</v>
+        <v>0.7167899094935493</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26">
-        <v>-0.01086160956316936</v>
+        <v>0.0001029551615340195</v>
       </c>
       <c r="D26">
-        <v>0.6409944155594071</v>
+        <v>-0.2172470633545158</v>
       </c>
       <c r="E26">
-        <v>-0.1149466535333391</v>
+        <v>0.001339924763424668</v>
       </c>
       <c r="F26">
-        <v>0.1893749576310764</v>
+        <v>0.9878342092151006</v>
       </c>
       <c r="G26">
-        <v>0.008232617683450377</v>
+        <v>0.00673900292442619</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>-0.7710148276526095</v>
+        <v>-0.2038628923550933</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <v>-0.01074279873794605</v>
+        <v>0.0003140114651379808</v>
       </c>
       <c r="D27">
-        <v>0.2346593491238206</v>
+        <v>0.1753435393799346</v>
       </c>
       <c r="E27">
-        <v>-0.09459117424017852</v>
+        <v>0.006428137812565618</v>
       </c>
       <c r="F27">
-        <v>0.28065262513802</v>
+        <v>0.9416851669160959</v>
       </c>
       <c r="G27">
-        <v>0.009916158944663573</v>
+        <v>0.004284298059560343</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>-1.161904486809166</v>
+        <v>0.2161650298478721</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28">
-        <v>-0.008968892048961372</v>
+        <v>0.002142102534476885</v>
       </c>
       <c r="D28">
-        <v>0.4190466653828873</v>
+        <v>0.1403924513768535</v>
       </c>
       <c r="E28">
-        <v>-0.09541306962247023</v>
+        <v>0.03031799801906173</v>
       </c>
       <c r="F28">
-        <v>0.2764753341809382</v>
+        <v>0.7300239932694141</v>
       </c>
       <c r="G28">
-        <v>0.008206790857740866</v>
+        <v>0.006193959612768919</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>-0.7469093009820911</v>
+        <v>0.4188657808588486</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>-0.008864252173784237</v>
+        <v>0.002265654455949085</v>
       </c>
       <c r="D29">
-        <v>0.5989905642210669</v>
+        <v>-0.04905943898838189</v>
       </c>
       <c r="E29">
-        <v>-0.0813703829927914</v>
+        <v>0.04589636280505199</v>
       </c>
       <c r="F29">
-        <v>0.3536555971947979</v>
+        <v>0.6012740623058614</v>
       </c>
       <c r="G29">
-        <v>0.009522731148012709</v>
+        <v>0.004324997199375741</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>-0.553362218370884</v>
+        <v>0.2454756402849991</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1394,25 +1394,25 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>-0.007303200067151539</v>
+        <v>0.003670225698301955</v>
       </c>
       <c r="D30">
-        <v>0.5755858527504973</v>
+        <v>0.1183597791899351</v>
       </c>
       <c r="E30">
-        <v>-0.06681667839469289</v>
+        <v>0.05196214474468448</v>
       </c>
       <c r="F30">
-        <v>0.4465286735177345</v>
+        <v>0.5540371913650939</v>
       </c>
       <c r="G30">
-        <v>0.009565001055725322</v>
+        <v>0.006186527143471792</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>-0.3738301559792027</v>
+        <v>0.5954891199691892</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1423,25 +1423,25 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>-0.007006447535390342</v>
+        <v>0.004017238195401109</v>
       </c>
       <c r="D31">
-        <v>0.591760575133192</v>
+        <v>0.1324403363502149</v>
       </c>
       <c r="E31">
-        <v>-0.06339042792373104</v>
+        <v>0.05499898980504644</v>
       </c>
       <c r="F31">
-        <v>0.4702328538852097</v>
+        <v>0.531082387003852</v>
       </c>
       <c r="G31">
-        <v>0.009674492315024669</v>
+        <v>0.006396513969990772</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>-0.3190776044675525</v>
+        <v>0.6546813017523591</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1452,25 +1452,25 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>-0.006418721454423364</v>
+        <v>0.004510221353202294</v>
       </c>
       <c r="D32">
-        <v>0.1261437832980296</v>
+        <v>-0.329228833686373</v>
       </c>
       <c r="E32">
-        <v>-0.05747180130174274</v>
+        <v>0.06044499162408692</v>
       </c>
       <c r="F32">
-        <v>0.5127499249559127</v>
+        <v>0.4911475259295794</v>
       </c>
       <c r="G32">
-        <v>0.00977920652551458</v>
+        <v>0.006532373938674796</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>-0.7082900057770077</v>
+        <v>0.2570999422299252</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1481,25 +1481,25 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.005724463404879348</v>
+        <v>0.00556958627738524</v>
       </c>
       <c r="D33">
-        <v>0.2182799922973233</v>
+        <v>-0.252305411130368</v>
       </c>
       <c r="E33">
-        <v>-0.06139690056706821</v>
+        <v>0.1135993624824425</v>
       </c>
       <c r="F33">
-        <v>0.4843347795269108</v>
+        <v>0.1946496386034447</v>
       </c>
       <c r="G33">
-        <v>0.008161999410810049</v>
+        <v>0.00427223252777852</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>-0.5259002503369919</v>
+        <v>0.4717408049297133</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,25 +1510,25 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>-0.00489731838224039</v>
+        <v>0.006125789647800046</v>
       </c>
       <c r="D34">
-        <v>-0.1439089800372297</v>
+        <v>-0.6032051479555811</v>
       </c>
       <c r="E34">
-        <v>-0.04372949492794493</v>
+        <v>0.08002854846138488</v>
       </c>
       <c r="F34">
-        <v>0.6185733080205327</v>
+        <v>0.361675545177081</v>
       </c>
       <c r="G34">
-        <v>0.009812881632502893</v>
+        <v>0.006691912543844372</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>-0.7805603697284804</v>
+        <v>0.1931475062584248</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,25 +1539,25 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>-0.004456768727132679</v>
+        <v>0.0068315039476218</v>
       </c>
       <c r="D35">
-        <v>0.5064394377046025</v>
+        <v>0.03609474292316578</v>
       </c>
       <c r="E35">
-        <v>-0.04294545397437286</v>
+        <v>0.1036473053127747</v>
       </c>
       <c r="F35">
-        <v>0.6248852444927793</v>
+        <v>0.2369363651746393</v>
       </c>
       <c r="G35">
-        <v>0.009093485253326818</v>
+        <v>0.005749647898008965</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>-0.07294049682264581</v>
+        <v>0.9241902561139996</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,25 +1568,25 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>-0.003423707456289775</v>
+        <v>0.007896916460521316</v>
       </c>
       <c r="D36">
-        <v>0.5321549521792155</v>
+        <v>0.06046228897875316</v>
       </c>
       <c r="E36">
-        <v>-0.03264974613172606</v>
+        <v>0.1164297167531187</v>
       </c>
       <c r="F36">
-        <v>0.7101547054189534</v>
+        <v>0.1836899817608382</v>
       </c>
       <c r="G36">
-        <v>0.009192075017750663</v>
+        <v>0.005908241939039064</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>0.08707298286154475</v>
+        <v>1.087061428846524</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>-0.003265620880178941</v>
+        <v>0.007985678946510836</v>
       </c>
       <c r="D37">
-        <v>-0.1042002695936837</v>
+        <v>-0.5730044290390911</v>
       </c>
       <c r="E37">
-        <v>-0.03384657014046923</v>
+        <v>0.1459073396220788</v>
       </c>
       <c r="F37">
-        <v>0.7000304878992039</v>
+        <v>0.09504808897702155</v>
       </c>
       <c r="G37">
-        <v>0.008457276273614908</v>
+        <v>0.004748869950020143</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>-0.5287309840169461</v>
+        <v>0.4651338340073176</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>-0.003253436825707188</v>
+        <v>0.008044656761814475</v>
       </c>
       <c r="D38">
-        <v>0.0788894024006675</v>
+        <v>-0.3918644970794019</v>
       </c>
       <c r="E38">
-        <v>-0.03534695764843575</v>
+        <v>0.1721316213277391</v>
       </c>
       <c r="F38">
-        <v>0.6874125905292188</v>
+        <v>0.048428524792955</v>
       </c>
       <c r="G38">
-        <v>0.008067652574073554</v>
+        <v>0.004037792730514598</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>-0.3440573849412669</v>
+        <v>0.6539408819564798</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,25 +1655,25 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>-0.00245753701975539</v>
+        <v>0.008893127336108277</v>
       </c>
       <c r="D39">
-        <v>0.2128266255857243</v>
+        <v>-0.2601177225752619</v>
       </c>
       <c r="E39">
-        <v>-0.02579645966558611</v>
+        <v>0.1673181119417665</v>
       </c>
       <c r="F39">
-        <v>0.7690569232918916</v>
+        <v>0.05516228788652781</v>
       </c>
       <c r="G39">
-        <v>0.008352639452420233</v>
+        <v>0.004595936827432475</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>-0.1066531869824763</v>
+        <v>0.895988831118814</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1684,25 +1684,25 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.0006460294182997867</v>
+        <v>0.01201575789894681</v>
       </c>
       <c r="D40">
-        <v>0.1900735605622951</v>
+        <v>-0.2836651261313307</v>
       </c>
       <c r="E40">
-        <v>0.006408425665928393</v>
+        <v>0.1926860555437586</v>
       </c>
       <c r="F40">
-        <v>0.9418636781165285</v>
+        <v>0.02686150649562132</v>
       </c>
       <c r="G40">
-        <v>0.008841385962717344</v>
+        <v>0.00536677643975568</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.2740573849412674</v>
+        <v>1.278383400731754</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,25 +1713,25 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.001063998380462854</v>
+        <v>0.01260530398416014</v>
       </c>
       <c r="D41">
-        <v>0.1004169715642851</v>
+        <v>-0.3804707619231019</v>
       </c>
       <c r="E41">
-        <v>0.01110318254212832</v>
+        <v>0.2205872399319384</v>
       </c>
       <c r="F41">
-        <v>0.8994497826074022</v>
+        <v>0.01103342291149403</v>
       </c>
       <c r="G41">
-        <v>0.008404174071393001</v>
+        <v>0.004888430319820599</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>0.2387367610244561</v>
+        <v>1.258218756017716</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1742,25 +1742,25 @@
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.00125957526650768</v>
+        <v>0.01266627659521941</v>
       </c>
       <c r="D42">
-        <v>-0.1428146864368704</v>
+        <v>-0.6180939084665256</v>
       </c>
       <c r="E42">
-        <v>0.01300134858355682</v>
+        <v>0.2210352658176881</v>
       </c>
       <c r="F42">
-        <v>0.882374618843337</v>
+        <v>0.01086745701242631</v>
       </c>
       <c r="G42">
-        <v>0.008496251055096028</v>
+        <v>0.004901609658678058</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.02093009820912803</v>
+        <v>1.028522048911997</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1771,25 +1771,25 @@
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.00127711366879478</v>
+        <v>0.01273234186059143</v>
       </c>
       <c r="D43">
-        <v>-0.1273631170164966</v>
+        <v>-0.6046642916746905</v>
       </c>
       <c r="E43">
-        <v>0.01354668431468313</v>
+        <v>0.2374788392213746</v>
       </c>
       <c r="F43">
-        <v>0.8774786124672767</v>
+        <v>0.006110142524849703</v>
       </c>
       <c r="G43">
-        <v>0.008267705790818673</v>
+        <v>0.004567794297529905</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.03866165992682474</v>
+        <v>1.050540150202196</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1800,25 +1800,25 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.001531937963827049</v>
+        <v>0.01292304137226148</v>
       </c>
       <c r="D44">
-        <v>0.06912651646447122</v>
+        <v>-0.4055027922202967</v>
       </c>
       <c r="E44">
-        <v>0.01524953984213023</v>
+        <v>0.2074382391391712</v>
       </c>
       <c r="F44">
-        <v>0.8622210484901547</v>
+        <v>0.01700326829077968</v>
       </c>
       <c r="G44">
-        <v>0.008809723147044599</v>
+        <v>0.005345068331278934</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>0.2682784517619876</v>
+        <v>1.274492586173696</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1829,25 +1829,25 @@
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.001654673204066622</v>
+        <v>0.01320753282278412</v>
       </c>
       <c r="D45">
-        <v>0.1544360998780407</v>
+        <v>-0.3269330509018552</v>
       </c>
       <c r="E45">
-        <v>0.01691062635014135</v>
+        <v>0.2186768361330113</v>
       </c>
       <c r="F45">
-        <v>0.8473864835681691</v>
+        <v>0.01176634516864738</v>
       </c>
       <c r="G45">
-        <v>0.008580621748813506</v>
+        <v>0.005169004007997702</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.3695436164067016</v>
+        <v>1.390046216060081</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1858,83 +1858,83 @@
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.001986808672423925</v>
+        <v>0.01341546262967407</v>
       </c>
       <c r="D46">
-        <v>0.10803491880095</v>
+        <v>-0.3681589960844729</v>
       </c>
       <c r="E46">
-        <v>0.0194703191124432</v>
+        <v>0.2057541668481952</v>
       </c>
       <c r="F46">
-        <v>0.8246328266021964</v>
+        <v>0.01794097630375603</v>
       </c>
       <c r="G46">
-        <v>0.008948061630305976</v>
+        <v>0.005596186723254141</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.3663200462160603</v>
+        <v>1.375851145773157</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.002156893648748073</v>
+        <v>0.01373312299100861</v>
       </c>
       <c r="D47">
-        <v>-0.111127928621863</v>
+        <v>-0.4643730021182362</v>
       </c>
       <c r="E47">
-        <v>0.02406719518175246</v>
+        <v>0.2247357166860495</v>
       </c>
       <c r="F47">
-        <v>0.784145527287415</v>
+        <v>0.009578467311875496</v>
       </c>
       <c r="G47">
-        <v>0.007857886667540061</v>
+        <v>0.005222417811384642</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.1692682457153865</v>
+        <v>1.320932986712883</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.002302158230754418</v>
+        <v>0.01396220849565737</v>
       </c>
       <c r="D48">
-        <v>0.01191719622568843</v>
+        <v>-0.6030160472430838</v>
       </c>
       <c r="E48">
-        <v>0.0231784903847785</v>
+        <v>0.2684797165930686</v>
       </c>
       <c r="F48">
-        <v>0.7919315821105954</v>
+        <v>0.001854391338985125</v>
       </c>
       <c r="G48">
-        <v>0.00870886693422857</v>
+        <v>0.004393654594027878</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.3111977662237628</v>
+        <v>1.212071057192375</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.003268334592424712</v>
+        <v>0.01486278866521501</v>
       </c>
       <c r="D49">
-        <v>0.06276526092817261</v>
+        <v>-0.4203369921047566</v>
       </c>
       <c r="E49">
-        <v>0.03235106579144525</v>
+        <v>0.225104659143009</v>
       </c>
       <c r="F49">
-        <v>0.7126892997860301</v>
+        <v>0.009457656160252704</v>
       </c>
       <c r="G49">
-        <v>0.008856025494381504</v>
+        <v>0.00564224919220108</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.4876487579433852</v>
+        <v>1.511825534373195</v>
       </c>
     </row>
   </sheetData>
